--- a/notes/shock_corpora_master_summary_updated.xlsx
+++ b/notes/shock_corpora_master_summary_updated.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Matthew\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\PythonProjects\AfD-project\notes\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{477FA69B-CB8F-4331-B670-FE2C7BBEA459}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{801B9742-C6BE-4585-893E-F16BBCFE6B38}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
